--- a/astro-site/public/dl/bar-business-plan/bar-financial-projections.xlsx
+++ b/astro-site/public/dl/bar-business-plan/bar-financial-projections.xlsx
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Build-out, installations, ventilation and decor of a bar with a commercial kitchen. Straight-line depreciation for the books; tax depreciation (MACRS, Section 179) can differ, so ask your CPA</t>
+          <t>Build-out, installations, ventilation and decor of a bar with a commercial kitchen, including the draft beer system. Straight-line depreciation for the books; tax depreciation (MACRS, Section 179) can differ, so ask your CPA</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Griddle, fryer, oven, refrigeration, draft beer system and bar furniture. Straight-line depreciation over the useful life you enter; tax depreciation (MACRS, Section 179) can differ, so confirm it with your CPA</t>
+          <t>Griddle, fryer, oven, refrigeration, the bar build and furniture. Straight-line depreciation over the useful life you enter; tax depreciation (MACRS, Section 179) can differ, so confirm it with your CPA</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TOTAL capacity of the space: dining room seats, bar stools and patio. Count it on your floor plan rather than copying the example: if your patio is large, capacity rises and the implied seat turns fall. Daily covers ÷ seats gives the implied seat turns in the row below</t>
+          <t>TOTAL capacity of the space: dining room seats and bar stools; add patio seats only if they are open most of the year. Count it on your floor plan rather than copying the example: counting a year-round patio raises capacity and lowers the implied seat turns. Daily covers ÷ seats gives the implied seat turns in the row below</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>You pay for the space from the day you sign. These months are a startup cost: they do NOT overlap the P&amp;L, which starts on opening day</t>
+          <t>You pay for the space from the day you sign. These months are a startup cost: they do NOT overlap the P&amp;L, which starts on opening day. If your liquor license is likely to take longer than the build-out (often 3-12 months from signing), enter the months until it is issued, or negotiate a license contingency and rent abatement in the lease.</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Same example rate as the rest of on-site sales (8%: state + local). Some states add a tax on drinks served on premises; e.g. Texas: 8.25% mixed beverage sales tax (paid by the customer) + 6.7% gross receipts tax (paid by the bar): put the first here and add the second to your beverage cost %. The workbook applies this rate only to the ALCOHOLIC part of beverage sales</t>
+          <t>Same example rate as the rest of on-site sales (8%: state + local). Some states add a tax on drinks served on premises; e.g. Texas: 8.25% mixed beverage sales tax (paid by the customer) + 6.7% gross receipts tax (paid by the bar): put the first here and add 6.7% × your alcohol share (about 6 points at 90%) to your beverage cost %. The workbook applies this rate only to the ALCOHOLIC part of beverage sales</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>Beer &amp; wine licenses start around $3,000; full liquor runs $12,000-$400,000. In quota states you buy an existing license at market price, which costs far more; this row is an example for a state WITHOUT a quota. A license bought from another owner is an intangible asset: ask your CPA. Apply right after signing the lease: it often takes 3-12 months</t>
+          <t>Beer &amp; wine licenses start around $3,000; full liquor runs $12,000-$400,000. In quota states you buy an existing license at market price, which costs far more; this row is an example for a state WITHOUT a quota. A license bought from another owner is an intangible asset: ask your CPA. Apply right after signing the lease: it often takes 3-12 months. Most states also charge an annual or biennial renewal fee: add it to your fixed costs</t>
         </is>
       </c>
       <c r="E8" s="32" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="E24" s="34" t="inlineStr">
         <is>
-          <t>Covers each full-time employee in the "5. Staffing" tab would have to serve. In the optimistic scenario it tells you whether you need to hire</t>
+          <t>Covers each full-time employee in the "Staffing" tab would have to serve. In the optimistic scenario it tells you whether you need to hire</t>
         </is>
       </c>
     </row>
@@ -5904,10 +5904,10 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="284.25" customHeight="1">
+    <row r="29" ht="194.5" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>The gross pay, employer payroll taxes, monthly cost and annual cost columns are TOTALS for the row: for a position with two people they include both. FTE is the share of a full-time week for each person, and it is used to compare pay with the legal minimum in proportion; the TOTAL row multiplies it by the people in each position, so it gives the full-time equivalents of the whole team. The payroll tax rate and the number of pay periods are in the "0. Assumptions" tab. Tips are not modeled: bartenders, barbacks and servers are budgeted at a base wage of at least $15/h. Federal rules allow a $2.13/h cash wage with a tip credit of up to $5.12 where the state permits it; CA, OR, WA, AK, MN, MT and NV do not (DOL)</t>
+          <t>The gross pay, employer payroll taxes, monthly cost and annual cost columns are TOTALS for the row: for a position with two people they include both. The payroll tax rate and the number of pay periods are in the "0. Assumptions" tab. Tips are not modeled: bartenders, barbacks and servers are budgeted at a base wage of at least $15/h. Federal rules allow a $2.13/h cash wage with a tip credit of up to $5.12 where the state permits it; CA, OR, WA, AK, MN, MT and NV do not (DOL)</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>US INDUSTRY BENCHMARKS</t>
+          <t>US INDUSTRY BENCHMARKS (sourced) AND KIT ESTIMATES</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
+    <row r="55" ht="45" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
           <t>Pour cost, whole bar</t>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="D55" s="17" t="inlineStr">
         <is>
-          <t>The beverage cost in this example (the "Beverage cost" row of "0. Assumptions") includes garnish and spillage</t>
+          <t>The beverage cost in this example (the "Cost of goods sold on BEVERAGE sales" row of "0. Assumptions") includes garnish and spillage</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="D69" s="17" t="inlineStr">
         <is>
-          <t>Enter your state's floor on "0. Assumptions"; there is no union agreement table to copy</t>
+          <t>Enter your state's floor on "0. Assumptions"; check your state and city rates at dol.gov</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/bar-business-plan/bar-financial-projections.xlsx
+++ b/astro-site/public/dl/bar-business-plan/bar-financial-projections.xlsx
@@ -2225,7 +2225,7 @@
         <v>0.03517873044870471</v>
       </c>
       <c r="D27" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (architect and MEP drawings, build-out, electrical and HVAC, plumbing, grease interceptor and hood, draft beer system, decor and lighting, signage), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (architect and MEP drawings, build-out, electrical and HVAC, plumbing, grease interceptor and hood, draft beer system, decor and lighting, signage), not of the whole block: the other items are left "&amp;"out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 10% of the BUILD-OUT items of this block (architect and MEP drawings, build-out, electrical and HVAC, plumbing, grease interceptor and hood, draft beer system, decor and lighting, signage), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E27" s="34" t="inlineStr">
@@ -2383,7 +2383,7 @@
         <v>34205.71428571429</v>
       </c>
       <c r="D37" s="38" t="str">
-        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, liquor license and local permits (a license bought from another owner is an intangible asset: ask your CPA), launch marketing, opening inventory, security deposit, pre-opening rent and the working capital reserve. They add up to "&amp;TEXT(B30-B35-B36,"#,##0")&amp;" of the "&amp;TEXT(B30,"#,##0")&amp;" total investment.","")</f>
+        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, liquor license and local permits (a license bought from another owner is an intangible asset: ask your CPA), launch marketing, opening inventory, security "&amp;"deposit, pre-opening rent and the working capital reserve. They add up to "&amp;TEXT(B30-B35-B36,"#,##0")&amp;" of the "&amp;TEXT(B30,"#,##0")&amp;" total investment.","")</f>
         <v>Not depreciated, because they are not fixed assets: LLC formation and legal, liquor license and local permits (a license bought from another owner is an intangible asset: ask your CPA), launch marketing, opening inventory, security deposit, pre-opening rent and the working capital reserve. They add up to 192732 of the 488932 total investment.</v>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="O20" s="29" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10, and the fourth quarter in Month 13: April, July, October and January when Month 1 is January): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/bar-business-plan/bar-financial-projections.xlsx
+++ b/astro-site/public/dl/bar-business-plan/bar-financial-projections.xlsx
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>How far planned sales must sit above cash break-even (fixed costs and the loan payment). The drop you can absorb is somewhat smaller: with a 15% cushion, about 13% of plan</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far planned sales sit above cash break-even. The drop you can absorb before you cannot pay the fixed costs and the loan payment is somewhat smaller: with a 25% cushion, 20%. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>
@@ -8565,7 +8565,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="48" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="29" t="n"/>

--- a/astro-site/public/dl/bar-business-plan/bar-financial-projections.xlsx
+++ b/astro-site/public/dl/bar-business-plan/bar-financial-projections.xlsx
@@ -1576,7 +1576,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>How far planned sales must sit above cash break-even (fixed costs and the loan payment). The drop you can absorb is somewhat smaller: with a 15% cushion, about 13% of plan</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
         <v>0.03517873044870471</v>
       </c>
       <c r="D27" t="str">
-        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (architect and MEP drawings, build-out, electrical and HVAC, plumbing, grease interceptor and hood, draft beer system, decor and lighting, signage), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
+        <f>IFERROR("At "&amp;TEXT('0. Assumptions'!$B$55,"0%")&amp;" of the BUILD-OUT items of this block (architect and MEP drawings, build-out, electrical and HVAC, plumbing, grease interceptor and hood, draft beer system, decor and lighting, signage), not of the whole block: the other items are left "&amp;"out. No lender funds a build-out without a cushion: the percentage is in ""0. Assumptions""","")</f>
         <v>At 10% of the BUILD-OUT items of this block (architect and MEP drawings, build-out, electrical and HVAC, plumbing, grease interceptor and hood, draft beer system, decor and lighting, signage), not of the whole block: the other items are left out. No lender funds a build-out without a cushion: the percentage is in "0. Assumptions"</v>
       </c>
       <c r="E27" s="34" t="inlineStr">
@@ -2383,7 +2383,7 @@
         <v>34205.71428571429</v>
       </c>
       <c r="D37" s="38" t="str">
-        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, liquor license and local permits (a license bought from another owner is an intangible asset: ask your CPA), launch marketing, opening inventory, security deposit, pre-opening rent and the working capital reserve. They add up to "&amp;TEXT(B30-B35-B36,"#,##0")&amp;" of the "&amp;TEXT(B30,"#,##0")&amp;" total investment.","")</f>
+        <f>IFERROR("Not depreciated, because they are not fixed assets: LLC formation and legal, liquor license and local permits (a license bought from another owner is an intangible asset: ask your CPA), launch marketing, opening inventory, security "&amp;"deposit, pre-opening rent and the working capital reserve. They add up to "&amp;TEXT(B30-B35-B36,"#,##0")&amp;" of the "&amp;TEXT(B30,"#,##0")&amp;" total investment.","")</f>
         <v>Not depreciated, because they are not fixed assets: LLC formation and legal, liquor license and local permits (a license bought from another owner is an intangible asset: ask your CPA), launch marketing, opening inventory, security deposit, pre-opening rent and the working capital reserve. They add up to 192732 of the 488932 total investment.</v>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far planned sales sit above cash break-even. The drop you can absorb before you cannot pay the fixed costs and the loan payment is somewhat smaller: with a 25% cushion, 20%. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="O20" s="29" t="inlineStr">
         <is>
-          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly (April, July, October, January): if your state requires monthly filing, expect smaller payments every month instead</t>
+          <t>Cash only leaves when the quarter's result is positive. Months without a settlement are left blank, not zero. The cell turns RED when the payment takes more cash than is left that month. The model settles quarterly, in the month after each plan quarter (Months 4, 7 and 10, and the fourth quarter in Month 13: April, July, October and January when Month 1 is January): if your state requires monthly filing, expect smaller payments every month instead</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="48" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="29" t="n"/>

--- a/astro-site/public/dl/bar-business-plan/bar-financial-projections.xlsx
+++ b/astro-site/public/dl/bar-business-plan/bar-financial-projections.xlsx
@@ -8562,7 +8562,7 @@
       <c r="N33" s="29" t="n"/>
       <c r="O33" s="29" t="n"/>
     </row>
-    <row r="34" ht="134.75" customHeight="1">
+    <row r="34" ht="149.5" customHeight="1">
       <c r="A34" s="48" t="inlineStr">
         <is>
           <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
